--- a/amostras/principal/P15/matriz_rastreabilidade_P15.xlsx
+++ b/amostras/principal/P15/matriz_rastreabilidade_P15.xlsx
@@ -1054,6 +1054,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1111,6 +1112,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1165,27 +1167,28 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Não Aplicável</t>
-        </is>
-      </c>
+          <t>Nenhuma</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Não Aplicável</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Amostra Não Preenchida</t>
+          <t>Nenhuma / Sem Achados</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Não Aplicável</t>
+          <t>Nenhuma</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Aguardando geração (Passo 1 pendente)</t>
+          <t>Não se aplica (amostra limpa)</t>
         </is>
       </c>
     </row>
@@ -1225,6 +1228,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1342,6 +1346,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1399,6 +1404,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1456,6 +1462,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1873,6 +1880,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1930,6 +1938,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1987,6 +1996,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Nenhum</t>
